--- a/src/main/java/com/crm/qa/testdata/freeCrmContacts.xlsx
+++ b/src/main/java/com/crm/qa/testdata/freeCrmContacts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejaskadu/git/FreeCRMTestAutomation/src/main/java/com/crm/qa/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0D8411-2074-2E44-84E3-94D3C3DC99FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CABB73-4EA0-1C48-9411-F99CA1039FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16360" xr2:uid="{B2A10FDB-C34D-384F-A1F8-3B50774882DF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>firstName</t>
   </si>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F37A21-51A6-BC4F-AF16-7CB44FCB05F2}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -475,34 +475,6 @@
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
         <v>17</v>
       </c>
     </row>
